--- a/stories/arbres/ATOM-LAN.SON.001-07.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Justine est à la gare avec papa. Un son long : tchou tchou. Papa dit : c'est un son. Quel nom ? Justine dit : le train. Un son : plic ploc, il pleut dehors. Justine dit le nom : la pluie. Un oiseau crie. Justine dit : l'oiseau. Papa dit : on entend un son. On dit le nom.</t>
+          <t>Justine est à la gare avec papa. Un son long : tchou tchou. C'est un son. Quel nom ? Le train. Un son : plic ploc, il pleut dehors. Justine dit le nom : la pluie. Un oiseau crie. L'oiseau. On entend un son. On dit le nom.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Justine est à la gare avec papa. Un son long : tchou tchou.
+papa|C'est un son. Quel nom ?
+enfant-f|Le train.
+narrateur|Un son : plic ploc, il pleut dehors. Justine dit le nom : la pluie. Un oiseau crie.
+enfant-f|L'oiseau.
+papa|On entend un son. On dit le nom.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Justine entend un bruit. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Justine a entendu un son. Elle a dit le nom. Train. Pluie. Oiseau.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1831,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa donne la main. Le train arrive.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1998,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-07.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 papa|On entend un son. On dit le nom.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|Justine entend un bruit. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Justine a entendu un son. Elle a dit le nom. Train. Pluie. Oiseau.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1844,7 @@
           <t>narrateur|Papa donne la main. Le train arrive.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2055,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.SON.001-07.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Justine nomme les sons de la gare</t>
+          <t>Le quai de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sur le quai, un ticket dépasse. Mila nomme le train, la pluie, l'oiseau. Papa donne la main.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Justine est à la gare avec papa. Un son long : tchou tchou. C'est un son. Quel nom ? Le train. Un son : plic ploc, il pleut dehors. Justine dit le nom : la pluie. Un oiseau crie. L'oiseau. On entend un son. On dit le nom.</t>
+          <t>Un ticket dépasse de la poche de papa. Le papier est un peu tiède. Le quai sent le pain chaud. Des flaques brillent entre les rails. Une horloge fait tic tic. Une valise roule, tout loin. Mila, on écoute ici. En ce moment, Mila tient la manche. Le banc du quai est froid. Un son long arrive. Tchou tchou. C'est un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Le train est encore loin. La vapeur sent le fer chaud. Il vient, papa. Oui. Dehors, un autre son. Plic ploc. La pluie tape le toit du quai. Encore un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Une goutte glisse sur le ticket. Mila tend l'oreille. Un oiseau crie sous la toiture. Cui cui. Un son. Quel nom ? L'oiseau. Oui. On entend un son. On dit le nom. Son. Nom. Mila répète tout bas. Train. Pluie. Oiseau. Bravo, Mila. Tu as dit le nom. Le pain du kiosque sent encore. Mila pose la main sur le banc. Il vibre un peu. Oui. Le train est encore loin. Le son a un nom. Le train. Oui. Une goutte tombe du toit. Elle fait un petit ploc dans la flaque. Tu as fini d'écouter ? Encore un peu. D'accord. L'horloge fait encore tic tic.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,66 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Justine est à la gare avec papa. Un son long : tchou tchou.
-papa|C'est un son. Quel nom ?
+          <t>narrateur|Un ticket dépasse de la poche de papa.
+narrateur|Le papier est un peu tiède.
+narrateur|Le quai sent le pain chaud.
+narrateur|Des flaques brillent entre les rails.
+narrateur|Une horloge fait tic tic.
+narrateur|Une valise roule, tout loin.
+papa|Mila, on écoute ici.
+narrateur|En ce moment, Mila tient la manche.
+narrateur|Le banc du quai est froid.
+narrateur|Un son long arrive.
+narrateur|Tchou tchou.
+papa|C'est un son.
+papa|Quel nom ?
 enfant-f|Le train.
-narrateur|Un son : plic ploc, il pleut dehors. Justine dit le nom : la pluie. Un oiseau crie.
+papa|Oui.
+papa|Le nom du son, c'est le train.
+narrateur|Le train est encore loin.
+narrateur|La vapeur sent le fer chaud.
+enfant-f|Il vient, papa.
+papa|Oui.
+narrateur|Dehors, un autre son.
+narrateur|Plic ploc.
+narrateur|La pluie tape le toit du quai.
+papa|Encore un son.
+papa|Quel nom ?
+enfant-f|La pluie.
+papa|Oui.
+papa|Le nom du son, c'est la pluie.
+narrateur|Une goutte glisse sur le ticket.
+narrateur|Mila tend l'oreille.
+narrateur|Un oiseau crie sous la toiture.
+narrateur|Cui cui.
+papa|Un son.
+papa|Quel nom ?
 enfant-f|L'oiseau.
-papa|On entend un son. On dit le nom.</t>
+papa|Oui.
+papa|On entend un son.
+papa|On dit le nom.
+enfant-f|Son.
+enfant-f|Nom.
+narrateur|Mila répète tout bas.
+enfant-f|Train.
+enfant-f|Pluie.
+enfant-f|Oiseau.
+papa|Bravo, Mila.
+papa|Tu as dit le nom.
+narrateur|Le pain du kiosque sent encore.
+narrateur|Mila pose la main sur le banc.
+enfant-f|Il vibre un peu.
+papa|Oui.
+papa|Le train est encore loin.
+papa|Le son a un nom.
+enfant-f|Le train.
+papa|Oui.
+narrateur|Une goutte tombe du toit.
+narrateur|Elle fait un petit ploc dans la flaque.
+papa|Tu as fini d'écouter ?
+enfant-f|Encore un peu.
+papa|D'accord.
+narrateur|L'horloge fait encore tic tic.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1345,7 +1411,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Justine entend un bruit. C'est quoi ?</t>
+          <t>Mila entend un bruit. C'est quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1501,7 +1567,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Justine entend un bruit. C'est quoi ?</t>
+          <t>narrateur|Mila entend un bruit.
+narrateur|C'est quoi ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1529,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Justine a entendu un son. Elle a dit le nom. Train. Pluie. Oiseau.</t>
+          <t>Mila a entendu un son. Elle a dit le nom. Train. Pluie. Oiseau. Tu as nommé le son ? Oui, papa. Bravo. Tu as fait du bon travail. Le tchou tchou se rapproche. La pluie fait des ronds dans une flaque. Mila pose le doigt sur le banc. Il est froid. Oui. On écoute encore. On dit le nom. Le train. Oui. L'oiseau se tait un moment. Mila sent le pain sur l'air. Ça sent bon. Oui. On a entendu des sons. On a dit les noms. Train, pluie, oiseau. Bravo. Une flaque tremble un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1673,7 +1740,33 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Justine a entendu un son. Elle a dit le nom. Train. Pluie. Oiseau.</t>
+          <t>narrateur|Mila a entendu un son.
+narrateur|Elle a dit le nom.
+narrateur|Train.
+narrateur|Pluie.
+narrateur|Oiseau.
+papa|Tu as nommé le son ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le tchou tchou se rapproche.
+narrateur|La pluie fait des ronds dans une flaque.
+narrateur|Mila pose le doigt sur le banc.
+enfant-f|Il est froid.
+papa|Oui.
+papa|On écoute encore.
+papa|On dit le nom.
+enfant-f|Le train.
+papa|Oui.
+narrateur|L'oiseau se tait un moment.
+narrateur|Mila sent le pain sur l'air.
+enfant-f|Ça sent bon.
+papa|Oui.
+papa|On a entendu des sons.
+papa|On a dit les noms.
+enfant-f|Train, pluie, oiseau.
+papa|Bravo.
+narrateur|Une flaque tremble un peu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1701,7 +1794,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa donne la main. Le train arrive.</t>
+          <t>Tu me donnes la main ? Oui. Papa prend la main de Mila. Le train arrive tout doux. Les roues font un long bruit. Tu as fini d'écouter le quai ? Oui, papa. Merci. Bravo. Le ticket reste dans la poche. La pluie tapote encore le toit. Tu as nommé le son, Mila. Oui. Le quai sent encore le fer chaud. La valise roule tout loin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1841,7 +1934,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa donne la main. Le train arrive.</t>
+          <t>papa|Tu me donnes la main ?
+enfant-f|Oui.
+narrateur|Papa prend la main de Mila.
+narrateur|Le train arrive tout doux.
+narrateur|Les roues font un long bruit.
+papa|Tu as fini d'écouter le quai ?
+enfant-f|Oui, papa.
+papa|Merci.
+papa|Bravo.
+narrateur|Le ticket reste dans la poche.
+narrateur|La pluie tapote encore le toit.
+papa|Tu as nommé le son, Mila.
+enfant-f|Oui.
+narrateur|Le quai sent encore le fer chaud.
+narrateur|La valise roule tout loin.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1869,7 +1976,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit le nom. Oui. Train, pluie, oiseau. Bravo, Mila. Le quai sent encore le pain. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2009,7 +2116,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai dit le nom.
+papa|Oui.
+papa|Train, pluie, oiseau.
+papa|Bravo, Mila.
+narrateur|Le quai sent encore le pain.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2031,7 +2143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2181,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-07.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-07.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Justine est à la gare avec papa. Un &lt;emphasis level="moderate"&gt;son&lt;/emphasis&gt; long : tchou tchou. Papa dit : c'est un son. Quel nom ? Justine dit : le train. Un son : plic ploc, il pleut dehors. Justine dit le nom : la pluie. Un oiseau crie. Justine dit : l'oiseau. Papa dit : on entend un son. On dit le nom.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un ticket dépasse de la poche de papa. Le papier est un peu tiède. Le quai sent le pain chaud. Des flaques brillent entre les rails. Une horloge fait tic tic. Une valise roule, tout loin. Mila, on écoute ici. En ce moment, Mila tient la manche. Le banc du quai est froid. Un son long arrive. Tchou tchou. C'est un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Le train est encore loin. La vapeur sent le fer chaud. Il vient, papa. Oui. Dehors, un autre son. Plic ploc. La pluie tape le toit du quai. Encore un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Une goutte glisse sur le ticket. Mila tend l'oreille. Un oiseau crie sous la toiture. Cui cui. Un son. Quel nom ? L'oiseau. Oui. On entend un son. On dit le nom. Son. Nom. Mila répète tout bas. Train. Pluie. Oiseau. Bravo, Mila. Tu as dit le nom. Le pain du kiosque sent encore. Mila pose la main sur le banc. Il vibre un peu. Oui. Le train est encore loin. Le son a un nom. Le train. Oui. Une goutte tombe du toit. Elle fait un petit ploc dans la flaque. Tu as fini d'écouter ? Encore un peu. D'accord. L'horloge fait encore tic tic.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1386,7 +1386,6 @@
 narrateur|L'horloge fait encore tic tic.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1416,7 +1415,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Justine entend un bruit. C'est quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila entend un bruit. C'est quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1571,7 +1570,6 @@
 narrateur|C'est quoi ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1596,12 +1594,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a entendu un son. Elle a dit le nom. Train. Pluie. Oiseau. Tu as nommé le son ? Oui, papa. Bravo. Tu as fait du bon travail. Le tchou tchou se rapproche. La pluie fait des ronds dans une flaque. Mila pose le doigt sur le banc. Il est froid. Oui. On écoute encore. On dit le nom. Le train. Oui. L'oiseau se tait un moment. Mila sent le pain sur l'air. Ça sent bon. Oui. On a entendu des sons. On a dit les noms. Train, pluie, oiseau. Bravo. Une flaque tremble un peu.</t>
+          <t>Mila a entendu un son. Elle a dit le nom. Train. Pluie. Oiseau. Tu as nommé le son ? Oui, papa. Bravo. Le tchou tchou se rapproche. La pluie fait des ronds dans une flaque. Mila pose le doigt sur le banc. Il est froid. Oui. On écoute encore. On dit le nom. Le train. Oui. L'oiseau se tait un moment. Mila sent le pain sur l'air. Ça sent bon. Oui. On a entendu des sons. On a dit les noms. Train, pluie, oiseau. Bravo. Une flaque tremble un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Justine a entendu un &lt;emphasis level="moderate"&gt;son&lt;/emphasis&gt;. Elle a dit le nom. Train. Pluie. Oiseau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a entendu un son. Elle a dit le nom. Train. Pluie. Oiseau. Tu as nommé le son ? Oui, papa. Bravo. Le tchou tchou se rapproche. La pluie fait des ronds dans une flaque. Mila pose le doigt sur le banc. Il est froid. Oui. On écoute encore. On dit le nom. Le train. Oui. L'oiseau se tait un moment. Mila sent le pain sur l'air. Ça sent bon. Oui. On a entendu des sons. On a dit les noms. Train, pluie, oiseau. Bravo. Une flaque tremble un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1748,7 +1746,6 @@
 papa|Tu as nommé le son ?
 enfant-f|Oui, papa.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 narrateur|Le tchou tchou se rapproche.
 narrateur|La pluie fait des ronds dans une flaque.
 narrateur|Mila pose le doigt sur le banc.
@@ -1769,7 +1766,6 @@
 narrateur|Une flaque tremble un peu.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,7 +1795,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;. Le train arrive.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Tu me donnes la main ? Oui. Papa prend la main de Mila. Le train arrive tout doux. Les roues font un long bruit. Tu as fini d'écouter le quai ? Oui, papa. Merci. Bravo. Le ticket reste dans la poche. La pluie tapote encore le toit. Tu as nommé le son, Mila. Oui. Le quai sent encore le fer chaud. La valise roule tout loin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1951,7 +1947,6 @@
 narrateur|La valise roule tout loin.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1976,12 +1971,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit le nom. Oui. Train, pluie, oiseau. Bravo, Mila. Le quai sent encore le pain. L'histoire est finie.</t>
+          <t>J'ai dit le nom. Oui. Train, pluie, oiseau. Bravo, Mila. Le quai sent encore le pain.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit le nom. Oui. Train, pluie, oiseau. Bravo, Mila. Le quai sent encore le pain.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2120,11 +2115,9 @@
 papa|Oui.
 papa|Train, pluie, oiseau.
 papa|Bravo, Mila.
-narrateur|Le quai sent encore le pain.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le quai sent encore le pain.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2143,7 +2136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2188,6 +2181,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-07.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Justine, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
